--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487104_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487104_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2204</v>
+        <v>2.0132</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5451</v>
+        <v>3.204</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.3247</v>
+        <v>-1.1908</v>
       </c>
       <c r="G2" t="n">
         <v>4.6432</v>
@@ -610,13 +610,13 @@
         <v>2.3161</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2069</v>
+        <v>-0.0003</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9466</v>
+        <v>0.6055</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7397</v>
+        <v>-0.6058</v>
       </c>
       <c r="V2" t="n">
         <v>-4.7527</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. MARTINEZ FERNANDEZ</t>
+          <t>E. GANDARILLAS GARMENDIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8706</v>
+        <v>1.2301</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0123</v>
+        <v>0.4591</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8829</v>
+        <v>0.771</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.829</v>
+        <v>2.9272</v>
       </c>
       <c r="H3" t="n">
-        <v>-5.5469</v>
+        <v>0.0569</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7179</v>
+        <v>2.8704</v>
       </c>
       <c r="J3" t="n">
-        <v>-4.4102</v>
+        <v>2.132</v>
       </c>
       <c r="K3" t="n">
-        <v>-5.3463</v>
+        <v>-0.497</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9361</v>
+        <v>2.629</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5812</v>
+        <v>0.7952</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2006</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7818000000000001</v>
+        <v>0.2413</v>
       </c>
       <c r="P3" t="n">
-        <v>2.3161</v>
+        <v>-0.965</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.193</v>
+        <v>-2.8951</v>
       </c>
       <c r="R3" t="n">
-        <v>2.5091</v>
+        <v>1.9301</v>
       </c>
       <c r="S3" t="n">
-        <v>3.1774</v>
+        <v>0.39</v>
       </c>
       <c r="T3" t="n">
-        <v>3.691</v>
+        <v>0.9363</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5135999999999999</v>
+        <v>-0.5463</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.794</v>
+        <v>-1.1221</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8999</v>
+        <v>0.2859</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.6938</v>
+        <v>-1.4079</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. GANDARILLAS GARMENDIA</t>
+          <t>M. CARCOBA BEDIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7839</v>
+        <v>-0.1696</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0397</v>
+        <v>-0.8241000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7442</v>
+        <v>0.6545</v>
       </c>
       <c r="G4" t="n">
-        <v>2.9272</v>
+        <v>1.8145</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0569</v>
+        <v>3.0419</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8704</v>
+        <v>-1.2274</v>
       </c>
       <c r="J4" t="n">
-        <v>2.132</v>
+        <v>3.3755</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.497</v>
+        <v>3.2291</v>
       </c>
       <c r="L4" t="n">
-        <v>2.629</v>
+        <v>0.1464</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7952</v>
+        <v>-1.561</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5538999999999999</v>
+        <v>-0.1872</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2413</v>
+        <v>-1.3738</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.8951</v>
+        <v>-4.0532</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9301</v>
+        <v>2.1231</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0562</v>
+        <v>-0.3821</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5169</v>
+        <v>-0.1464</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5731000000000001</v>
+        <v>-0.2357</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.1221</v>
+        <v>0.3281</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.4079</v>
+        <v>0.3281</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. CARCOBA BEDIA</t>
+          <t>D. TRUEBA TAMAYO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.09619999999999999</v>
+        <v>-0.4049</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.724</v>
+        <v>0.1419</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6278</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8145</v>
+        <v>-0.6781</v>
       </c>
       <c r="H5" t="n">
-        <v>3.0419</v>
+        <v>0.2516</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.2274</v>
+        <v>-0.9297</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3755</v>
+        <v>-0.4984</v>
       </c>
       <c r="K5" t="n">
-        <v>3.2291</v>
+        <v>0.1449</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1464</v>
+        <v>-0.6433</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.561</v>
+        <v>-0.1797</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1872</v>
+        <v>0.1067</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.3738</v>
+        <v>-0.2863</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.9301</v>
+        <v>-0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.0532</v>
+        <v>-0.965</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1231</v>
+        <v>0.965</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3087</v>
+        <v>0.4531</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0462</v>
+        <v>0.3774</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2624</v>
+        <v>0.0757</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3281</v>
+        <v>-0.18</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3281</v>
+        <v>-1.4079</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. GOMEZ MERODIO</t>
+          <t>D. GARCIA CARRERA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6556</v>
+        <v>-0.5276</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0576</v>
+        <v>1.1763</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5981</v>
+        <v>-1.7039</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.152</v>
+        <v>1.2601</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0528</v>
+        <v>1.7492</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0993</v>
+        <v>-0.4891</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0614</v>
+        <v>2.9407</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0207</v>
+        <v>1.7697</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0407</v>
+        <v>1.171</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2134</v>
+        <v>-1.6806</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0735</v>
+        <v>-0.0205</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.14</v>
+        <v>-1.6601</v>
       </c>
       <c r="P6" t="n">
-        <v>0.193</v>
+        <v>1.158</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.1231</v>
       </c>
       <c r="R6" t="n">
-        <v>0.193</v>
+        <v>3.2811</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.08260000000000001</v>
+        <v>-0.2039</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.119</v>
+        <v>0.4009</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0363</v>
+        <v>-0.6049</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.614</v>
+        <v>-2.7418</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.0422</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.614</v>
+        <v>-2.6996</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. GARCIA CARRERA</t>
+          <t>J. GOMEZ MERODIO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7863</v>
+        <v>-0.7359</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7569</v>
+        <v>-0.0576</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.5432</v>
+        <v>-0.6784</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2601</v>
+        <v>-0.152</v>
       </c>
       <c r="H7" t="n">
-        <v>1.7492</v>
+        <v>-0.0528</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4891</v>
+        <v>-0.0993</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9407</v>
+        <v>0.0614</v>
       </c>
       <c r="K7" t="n">
-        <v>1.7697</v>
+        <v>0.0207</v>
       </c>
       <c r="L7" t="n">
-        <v>1.171</v>
+        <v>0.0407</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.6806</v>
+        <v>-0.2134</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0205</v>
+        <v>-0.0735</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.6601</v>
+        <v>-0.14</v>
       </c>
       <c r="P7" t="n">
-        <v>1.158</v>
+        <v>0.193</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1231</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.2811</v>
+        <v>0.193</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4627</v>
+        <v>-0.1629</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0185</v>
+        <v>-0.119</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4442</v>
+        <v>-0.044</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.7418</v>
+        <v>-0.614</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.0422</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.6996</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. TRUEBA TAMAYO</t>
+          <t>S. MARTINEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.979</v>
+        <v>-1.046</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4589</v>
+        <v>-1.9556</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5201</v>
+        <v>0.9097</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6781</v>
+        <v>-3.829</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2516</v>
+        <v>-5.5469</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9297</v>
+        <v>1.7179</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4984</v>
+        <v>-4.4102</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1449</v>
+        <v>-5.3463</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6433</v>
+        <v>0.9361</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1797</v>
+        <v>0.5812</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1067</v>
+        <v>-0.2006</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2863</v>
+        <v>0.7818000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>-0</v>
+        <v>2.3161</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.965</v>
+        <v>-0.193</v>
       </c>
       <c r="R8" t="n">
-        <v>0.965</v>
+        <v>2.5091</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.121</v>
+        <v>1.2608</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2234</v>
+        <v>1.7477</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1024</v>
+        <v>-0.4869</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.18</v>
+        <v>-0.794</v>
       </c>
       <c r="W8" t="n">
-        <v>1.228</v>
+        <v>0.8999</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.4079</v>
+        <v>-1.6938</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. UGARTE JAUREGUI</t>
+          <t>A. QUINCY-JONES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6812</v>
+        <v>-1.7612</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3391</v>
+        <v>-0.9738</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3422</v>
+        <v>-0.7875</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.5955</v>
+        <v>0.4535</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.6758</v>
+        <v>1.9023</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9197</v>
+        <v>-1.4488</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4613</v>
+        <v>1.7673</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.502</v>
+        <v>1.7023</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0407</v>
+        <v>0.065</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1341</v>
+        <v>-1.3138</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1738</v>
+        <v>0.1999</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9604</v>
+        <v>-1.5137</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9301</v>
+        <v>-3.8602</v>
       </c>
       <c r="R9" t="n">
-        <v>0.965</v>
+        <v>1.9301</v>
       </c>
       <c r="S9" t="n">
-        <v>1.3451</v>
+        <v>0.2234</v>
       </c>
       <c r="T9" t="n">
-        <v>1.0523</v>
+        <v>0.5473</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2928</v>
+        <v>-0.3239</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.4658</v>
+        <v>-0.5081</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.5717</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.4658</v>
+        <v>-1.0798</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. QUINCY-JONES</t>
+          <t>J. UGARTE JAUREGUI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2213</v>
+        <v>-2.2097</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4338</v>
+        <v>-1.6802</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7875</v>
+        <v>-0.5295</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4535</v>
+        <v>-1.5955</v>
       </c>
       <c r="H10" t="n">
-        <v>1.9023</v>
+        <v>-0.6758</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.4488</v>
+        <v>-0.9197</v>
       </c>
       <c r="J10" t="n">
-        <v>1.7673</v>
+        <v>-0.4613</v>
       </c>
       <c r="K10" t="n">
-        <v>1.7023</v>
+        <v>-0.502</v>
       </c>
       <c r="L10" t="n">
-        <v>0.065</v>
+        <v>0.0407</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3138</v>
+        <v>-1.1341</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1999</v>
+        <v>-0.1738</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.5137</v>
+        <v>-0.9604</v>
       </c>
       <c r="P10" t="n">
+        <v>-0.965</v>
+      </c>
+      <c r="Q10" t="n">
         <v>-1.9301</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-3.8602</v>
-      </c>
       <c r="R10" t="n">
-        <v>1.9301</v>
+        <v>0.965</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2366</v>
+        <v>0.8166</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0873</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3239</v>
+        <v>0.1054</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5081</v>
+        <v>-0.4658</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5717</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0798</v>
+        <v>-0.4658</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.5167</v>
+        <v>-2.855</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.352</v>
+        <v>-2.9312</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1647</v>
+        <v>0.0762</v>
       </c>
       <c r="G11" t="n">
         <v>-2.0393</v>
@@ -1312,13 +1312,13 @@
         <v>3.0881</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.1264</v>
+        <v>-0.4647</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1607</v>
+        <v>0.2601</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9657</v>
+        <v>-0.7248</v>
       </c>
       <c r="V11" t="n">
         <v>0.614</v>
@@ -1345,22 +1345,22 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.0614</v>
+        <v>-6.466600000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.036</v>
+        <v>-3.4412</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.025599999999999</v>
+        <v>-3.0256</v>
       </c>
       <c r="G12" t="n">
-        <v>2.8046</v>
+        <v>2.804600000000002</v>
       </c>
       <c r="H12" t="n">
         <v>2.8047</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0002000000000008662</v>
+        <v>-0.000199999999999978</v>
       </c>
       <c r="J12" t="n">
         <v>9.671400000000002</v>
@@ -1381,7 +1381,7 @@
         <v>-6.997599999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.965</v>
+        <v>-0.9649999999999996</v>
       </c>
       <c r="Q12" t="n">
         <v>-20.2659</v>
@@ -1390,13 +1390,13 @@
         <v>19.3007</v>
       </c>
       <c r="S12" t="n">
-        <v>1.3352</v>
+        <v>1.93</v>
       </c>
       <c r="T12" t="n">
-        <v>4.726299999999999</v>
+        <v>5.321</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.3911</v>
+        <v>-3.3912</v>
       </c>
       <c r="V12" t="n">
         <v>-10.2364</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.4146</v>
+        <v>6.9757</v>
       </c>
       <c r="E13" t="n">
-        <v>6.2567</v>
+        <v>6.6573</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1578</v>
+        <v>0.3185</v>
       </c>
       <c r="G13" t="n">
         <v>5.7362</v>
@@ -1468,13 +1468,13 @@
         <v>1.3511</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.3708</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4019</v>
+        <v>-0.0013</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5301</v>
+        <v>-0.3695</v>
       </c>
       <c r="V13" t="n">
         <v>3.1544</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.3193</v>
+        <v>5.7929</v>
       </c>
       <c r="E14" t="n">
-        <v>5.5487</v>
+        <v>6.0494</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2294</v>
+        <v>-0.2565</v>
       </c>
       <c r="G14" t="n">
         <v>0.579</v>
@@ -1546,13 +1546,13 @@
         <v>3.0881</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8038</v>
+        <v>-0.3302</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.033</v>
+        <v>0.4677</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7708</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>2.4559</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.265</v>
+        <v>5.2773</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9329</v>
+        <v>1.1332</v>
       </c>
       <c r="F15" t="n">
-        <v>4.3321</v>
+        <v>4.1441</v>
       </c>
       <c r="G15" t="n">
         <v>1.4949</v>
@@ -1624,13 +1624,13 @@
         <v>2.3161</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7978</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2948</v>
+        <v>0.4951</v>
       </c>
       <c r="U15" t="n">
-        <v>0.503</v>
+        <v>0.3149</v>
       </c>
       <c r="V15" t="n">
         <v>0.6562</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. HERNANDO PEREZ</t>
+          <t>D. ARRIBAS RODRIGUEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4961</v>
+        <v>0.7287</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6013</v>
+        <v>0.6601</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1052</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.1812</v>
+        <v>1.3237</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.2854</v>
+        <v>0.9574</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1042</v>
+        <v>0.3663</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1076</v>
+        <v>0.8095</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.2434</v>
+        <v>0.7038</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3509</v>
+        <v>0.1057</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.2887</v>
+        <v>0.5142</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.042</v>
+        <v>0.2536</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.2467</v>
+        <v>0.2606</v>
       </c>
       <c r="P16" t="n">
-        <v>0.772</v>
+        <v>1.3511</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.7021</v>
+        <v>1.3511</v>
       </c>
       <c r="S16" t="n">
-        <v>1.5771</v>
+        <v>-0.1041</v>
       </c>
       <c r="T16" t="n">
-        <v>1.8521</v>
+        <v>-0.1494</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.275</v>
+        <v>0.0453</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3281</v>
+        <v>-1.842</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5717</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2436</v>
+        <v>-1.842</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. ARRIBAS RODRIGUEZ</t>
+          <t>W. DIAZ GONZALEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4078</v>
+        <v>0.0526</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6601</v>
+        <v>-0.7964</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2523</v>
+        <v>0.849</v>
       </c>
       <c r="G17" t="n">
-        <v>1.3237</v>
+        <v>-1.4321</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9574</v>
+        <v>-1.1457</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3663</v>
+        <v>-0.2863</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8095</v>
+        <v>-0.5848</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7038</v>
+        <v>-0.5848</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1057</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5142</v>
+        <v>-0.8473000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2536</v>
+        <v>-0.5609</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2606</v>
+        <v>-0.2863</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3511</v>
+        <v>-1.158</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3511</v>
+        <v>0.772</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.425</v>
+        <v>0.5149</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1494</v>
+        <v>0.2469</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2756</v>
+        <v>0.268</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.842</v>
+        <v>2.1278</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.4716</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.842</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>W. DIAZ GONZALEZ</t>
+          <t>M. HERNANDO PEREZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0743</v>
+        <v>-0.047</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8965</v>
+        <v>0.2995</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8223</v>
+        <v>-0.3465</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.4321</v>
+        <v>-1.1812</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.1457</v>
+        <v>-1.2854</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2863</v>
+        <v>0.1042</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5848</v>
+        <v>1.1076</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5848</v>
+        <v>-0.2434</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.3509</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8473000000000001</v>
+        <v>-2.2887</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5609</v>
+        <v>-1.042</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2863</v>
+        <v>-1.2467</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.158</v>
+        <v>0.772</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R18" t="n">
-        <v>0.772</v>
+        <v>2.7021</v>
       </c>
       <c r="S18" t="n">
-        <v>0.388</v>
+        <v>0.034</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1468</v>
+        <v>0.5503</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2413</v>
+        <v>-0.5163</v>
       </c>
       <c r="V18" t="n">
-        <v>2.1278</v>
+        <v>0.3281</v>
       </c>
       <c r="W18" t="n">
-        <v>1.4716</v>
+        <v>0.5717</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6562</v>
+        <v>-0.2436</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4729</v>
+        <v>-0.3529</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0964</v>
+        <v>0.1039</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3765</v>
+        <v>-0.4568</v>
       </c>
       <c r="G19" t="n">
         <v>-0.5383</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0654</v>
+        <v>0.1854</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1785</v>
+        <v>0.0218</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2439</v>
+        <v>0.1636</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9771</v>
+        <v>-1.1479</v>
       </c>
       <c r="E20" t="n">
         <v>-2.3006</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3236</v>
+        <v>1.1528</v>
       </c>
       <c r="G20" t="n">
         <v>-2.3056</v>
@@ -2014,13 +2014,13 @@
         <v>3.6672</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.4086</v>
+        <v>-0.5794</v>
       </c>
       <c r="T20" t="n">
         <v>0.6346000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>-2.0431</v>
+        <v>-1.2139</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6167</v>
+        <v>-1.3473</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9511</v>
+        <v>-2.3502</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3343</v>
+        <v>1.0029</v>
       </c>
       <c r="G21" t="n">
         <v>-5.1038</v>
@@ -2092,13 +2092,13 @@
         <v>3.6672</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.6637</v>
+        <v>-0.3943</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.152</v>
+        <v>0.4489</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.5117</v>
+        <v>-0.8431</v>
       </c>
       <c r="V21" t="n">
         <v>2.4137</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.7003</v>
+        <v>-7.5354</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.7296</v>
+        <v>-6.4306</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9707</v>
+        <v>-1.1048</v>
       </c>
       <c r="G22" t="n">
         <v>-1.3775</v>
@@ -2170,13 +2170,13 @@
         <v>1.3511</v>
       </c>
       <c r="S22" t="n">
-        <v>1.0695</v>
+        <v>0.2343</v>
       </c>
       <c r="T22" t="n">
-        <v>1.3775</v>
+        <v>0.6766</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3081</v>
+        <v>-0.4422</v>
       </c>
       <c r="V22" t="n">
         <v>0.9421</v>
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>7.061500000000002</v>
+        <v>8.396699999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>3.025500000000001</v>
+        <v>3.025600000000003</v>
       </c>
       <c r="F23" t="n">
-        <v>4.036</v>
+        <v>5.371300000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.8047</v>
+        <v>-2.804699999999999</v>
       </c>
       <c r="H23" t="n">
         <v>-2.8047</v>
@@ -2224,7 +2224,7 @@
         <v>6.867</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.1307999999999999</v>
+        <v>-0.1308000000000001</v>
       </c>
       <c r="L23" t="n">
         <v>6.997599999999998</v>
@@ -2248,13 +2248,13 @@
         <v>20.266</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3353</v>
+        <v>-0.0001999999999999225</v>
       </c>
       <c r="T23" t="n">
-        <v>3.391</v>
+        <v>3.3912</v>
       </c>
       <c r="U23" t="n">
-        <v>-4.7262</v>
+        <v>-3.3911</v>
       </c>
       <c r="V23" t="n">
         <v>10.2362</v>
